--- a/order_forms/040_music_and_video_package_request--order_forms.xlsx
+++ b/order_forms/040_music_and_video_package_request--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>package_option_0</t>
+          <t>event_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Package 1</t>
+          <t>Event Time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>package_option_1</t>
+          <t>package_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Package 2</t>
+          <t>Package Type</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>package_option_2</t>
+          <t>client_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Package 3</t>
+          <t>Client Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>client_preference_0</t>
+          <t>event_description</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Package 1</t>
+          <t>Event Description</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>client_preference_1</t>
+          <t>client_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Package 2</t>
+          <t>Client Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>client_preference_2</t>
+          <t>package_details</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Package 3</t>
+          <t>Package Details</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,46 +722,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_details_form</t>
+          <t>event_venue</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event Details Form</t>
+          <t>Event Venue</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>client_preferences_0</t>
+          <t>event_details_form</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Package 1</t>
+          <t>Event Details Form</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>client_preferences_1</t>
+          <t>client_preferences_0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Package 2</t>
+          <t>Package 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>client_preferences_2</t>
+          <t>client_preferences_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Package 3</t>
+          <t>Package 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>package_details</t>
+          <t>client_preferences_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Package Details</t>
+          <t>Package 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,41 +842,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>package_type</t>
+          <t>client_preferences_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Package Type</t>
+          <t>Client Preferences</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>client_preferences_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Event Time</t>
+          <t>Package 1 Preference</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>event_venue</t>
+          <t>client_preferences_5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Event Venue</t>
+          <t>Package 2 Preference</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,108 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>event_description</t>
+          <t>client_preferences_6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Event Description</t>
+          <t>Package 3 Preference</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>client_email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Client Email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>client_phone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Client Phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>client_name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Client Name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>client_address</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Client Address</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
